--- a/EBS명의_2016-2020.xlsx
+++ b/EBS명의_2016-2020.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2016" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2017" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2019" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2020" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2016" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2017" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2018" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2019" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2020" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="안내" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2016'!$A$1:$E$52</definedName>
@@ -27,10 +27,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -79,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -87,10 +85,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -458,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -516,8 +517,13 @@
           <t>무릎 관절염</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>42377</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.snuh.org</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -541,8 +547,13 @@
           <t>위암</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>42384</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://sev.severance.healthcare</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -566,8 +577,13 @@
           <t>파킨슨병</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>42391</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -591,8 +607,13 @@
           <t>대장질환·대장암</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>42398</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.samsungsanhospital.com</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -616,8 +637,13 @@
           <t>폐암</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>42405</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.amc.seoul.kr</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -641,8 +667,13 @@
           <t>노년층 폐질환</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>42412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://sev.severance.healthcare</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -666,8 +697,13 @@
           <t>구강암</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>42419</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.snuh.org</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -691,8 +727,13 @@
           <t>자궁·난소 질환</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>42426</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.samsungsanhospital.com</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -716,8 +757,13 @@
           <t>유방암</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="5" t="n">
         <v>42433</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.ncc.re.kr</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -741,8 +787,13 @@
           <t>관절염</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="5" t="n">
         <v>42440</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -766,8 +817,13 @@
           <t>신장질환·신장이식</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="5" t="n">
         <v>42447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.cmcseoul.or.kr</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -791,8 +847,13 @@
           <t>간질환·간이식</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="5" t="n">
         <v>42454</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.snuh.org</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -816,8 +877,13 @@
           <t>척추질환</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="5" t="n">
         <v>42461</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.khmc.or.kr</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -841,8 +907,13 @@
           <t>화병·우울증</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="5" t="n">
         <v>42468</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.khmc.or.kr</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -866,8 +937,13 @@
           <t>뇌종양</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="5" t="n">
         <v>42475</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.samsungsanhospital.com</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -891,8 +967,13 @@
           <t>신경통</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="5" t="n">
         <v>42482</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.snuh.org</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -916,8 +997,13 @@
           <t>코·인두·후두 질환</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="5" t="n">
         <v>42489</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.cmcseoul.or.kr</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -941,8 +1027,13 @@
           <t>치매</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="5" t="n">
         <v>42496</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -966,8 +1057,13 @@
           <t>심장질환</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="5" t="n">
         <v>42503</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.samsungsanhospital.com</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -991,8 +1087,13 @@
           <t>당뇨 합병증</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="5" t="n">
         <v>42510</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.amc.seoul.kr</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1016,8 +1117,13 @@
           <t>췌장암</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="5" t="n">
         <v>42517</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.snuh.org</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1041,8 +1147,13 @@
           <t>지방간·간질환</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="5" t="n">
         <v>42524</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.ajoumc.or.kr</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1066,8 +1177,13 @@
           <t>비뇨기암</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="5" t="n">
         <v>42531</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://sev.severance.healthcare</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1091,8 +1207,13 @@
           <t>척추·디스크</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="5" t="n">
         <v>42538</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1116,8 +1237,13 @@
           <t>피부암</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="5" t="n">
         <v>42545</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1141,8 +1267,13 @@
           <t>두통</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="5" t="n">
         <v>42552</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.samsungsanhospital.com</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1166,8 +1297,13 @@
           <t>난청·이명·어지럼증</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="5" t="n">
         <v>42559</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1191,8 +1327,13 @@
           <t>간질환·간이식</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="5" t="n">
         <v>42566</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.amc.seoul.kr</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1216,8 +1357,13 @@
           <t>대장암</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="5" t="n">
         <v>42573</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://sev.severance.healthcare</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1241,8 +1387,13 @@
           <t>심장질환</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="5" t="n">
         <v>42580</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.samsungsanhospital.com</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1266,8 +1417,13 @@
           <t>유방암</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="5" t="n">
         <v>42587</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.snuh.org</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1291,8 +1447,13 @@
           <t>폐암</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="5" t="n">
         <v>42594</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1316,8 +1477,13 @@
           <t>위암</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="5" t="n">
         <v>42601</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://sev.severance.healthcare</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1341,8 +1507,13 @@
           <t>척추질환</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="5" t="n">
         <v>42615</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.khnmc.or.kr</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1366,8 +1537,13 @@
           <t>뇌혈관질환</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="5" t="n">
         <v>42622</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.snubh.org</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1391,8 +1567,13 @@
           <t>무릎질환</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="5" t="n">
         <v>42629</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.khmc.or.kr</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1416,8 +1597,13 @@
           <t>췌장암</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="5" t="n">
         <v>42636</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.snuh.org</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1441,8 +1627,13 @@
           <t>손 신경질환</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="5" t="n">
         <v>42643</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1466,8 +1657,13 @@
           <t>뇌전증</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="5" t="n">
         <v>42650</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://sev.severance.healthcare</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1491,8 +1687,13 @@
           <t>배뇨장애</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="5" t="n">
         <v>42657</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.samsungsanhospital.com</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1516,8 +1717,13 @@
           <t>요로결석</t>
         </is>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="5" t="n">
         <v>42664</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1541,8 +1747,13 @@
           <t>COPD</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="5" t="n">
         <v>42671</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1566,8 +1777,13 @@
           <t>흉부 통증</t>
         </is>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="5" t="n">
         <v>42678</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.khnmc.or.kr</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1591,8 +1807,13 @@
           <t>노안·실명질환</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="5" t="n">
         <v>42685</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.samsungsanhospital.com</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1616,8 +1837,13 @@
           <t>류마티스 질환</t>
         </is>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="5" t="n">
         <v>42692</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1641,8 +1867,13 @@
           <t>항암·암 치료</t>
         </is>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="5" t="n">
         <v>42699</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.snuh.org</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1666,8 +1897,13 @@
           <t>당뇨발</t>
         </is>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="5" t="n">
         <v>42706</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1691,8 +1927,13 @@
           <t>호르몬 질환</t>
         </is>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="5" t="n">
         <v>42713</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://sev.severance.healthcare</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1716,8 +1957,13 @@
           <t>임플란트·치주질환</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="5" t="n">
         <v>42720</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1741,8 +1987,13 @@
           <t>난임</t>
         </is>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="5" t="n">
         <v>42727</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://sev.severance.healthcare</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1766,8 +2017,13 @@
           <t>뇌동맥·대동맥류</t>
         </is>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="5" t="n">
         <v>42734</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.snuh.org</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1840,7 +2096,7 @@
           <t>심부전</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>42741</v>
       </c>
     </row>
@@ -1865,7 +2121,7 @@
           <t>폐·식도 수술</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>42748</v>
       </c>
     </row>
@@ -1890,7 +2146,7 @@
           <t>폐경</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>42755</v>
       </c>
     </row>
@@ -1915,7 +2171,7 @@
           <t>골반저질환</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>42762</v>
       </c>
     </row>
@@ -1940,7 +2196,7 @@
           <t>뇌졸중 재활</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>42769</v>
       </c>
     </row>
@@ -1965,7 +2221,7 @@
           <t>부정맥</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>42776</v>
       </c>
     </row>
@@ -1990,7 +2246,7 @@
           <t>당뇨·대사수술</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>42783</v>
       </c>
     </row>
@@ -2015,7 +2271,7 @@
           <t>신장질환</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>42797</v>
       </c>
     </row>
@@ -2040,7 +2296,7 @@
           <t>간경변</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="5" t="n">
         <v>42804</v>
       </c>
     </row>
@@ -2065,7 +2321,7 @@
           <t>수면장애</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="5" t="n">
         <v>42811</v>
       </c>
     </row>
@@ -2090,7 +2346,7 @@
           <t>인공관절</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="5" t="n">
         <v>42818</v>
       </c>
     </row>
@@ -2115,7 +2371,7 @@
           <t>뇌종양</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="5" t="n">
         <v>42825</v>
       </c>
     </row>
@@ -2140,7 +2396,7 @@
           <t>다리 혈관질환</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="5" t="n">
         <v>42832</v>
       </c>
     </row>
@@ -2165,7 +2421,7 @@
           <t>대장암</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="5" t="n">
         <v>42839</v>
       </c>
     </row>
@@ -2190,7 +2446,7 @@
           <t>고지혈증</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="5" t="n">
         <v>42846</v>
       </c>
     </row>
@@ -2215,7 +2471,7 @@
           <t>미세먼지 질환</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="5" t="n">
         <v>42853</v>
       </c>
     </row>
@@ -2240,7 +2496,7 @@
           <t>어깨질환</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="5" t="n">
         <v>42860</v>
       </c>
     </row>
@@ -2265,7 +2521,7 @@
           <t>위암</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="5" t="n">
         <v>42867</v>
       </c>
     </row>
@@ -2290,7 +2546,7 @@
           <t>심장질환·스텐트</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="5" t="n">
         <v>42874</v>
       </c>
     </row>
@@ -2315,7 +2571,7 @@
           <t>혈액암</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="5" t="n">
         <v>42881</v>
       </c>
     </row>
@@ -2340,7 +2596,7 @@
           <t>비흡연 폐암</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="5" t="n">
         <v>42888</v>
       </c>
     </row>
@@ -2365,7 +2621,7 @@
           <t>고혈압</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="5" t="n">
         <v>42895</v>
       </c>
     </row>
@@ -2390,7 +2646,7 @@
           <t>구강암</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="5" t="n">
         <v>42902</v>
       </c>
     </row>
@@ -2415,7 +2671,7 @@
           <t>파킨슨병</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="5" t="n">
         <v>42909</v>
       </c>
     </row>
@@ -2440,7 +2696,7 @@
           <t>지방간</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="5" t="n">
         <v>42916</v>
       </c>
     </row>
@@ -2465,7 +2721,7 @@
           <t>척추·척수 종양</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="5" t="n">
         <v>42923</v>
       </c>
     </row>
@@ -2490,7 +2746,7 @@
           <t>호르몬·비만</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="5" t="n">
         <v>42930</v>
       </c>
     </row>
@@ -2515,7 +2771,7 @@
           <t>췌장암</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="5" t="n">
         <v>42937</v>
       </c>
     </row>
@@ -2540,7 +2796,7 @@
           <t>귀 질환·난청</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="5" t="n">
         <v>42944</v>
       </c>
     </row>
@@ -2565,7 +2821,7 @@
           <t>대상포진</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="5" t="n">
         <v>42951</v>
       </c>
     </row>
@@ -2590,7 +2846,7 @@
           <t>발 질환</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="5" t="n">
         <v>42958</v>
       </c>
     </row>
@@ -2615,7 +2871,7 @@
           <t>류마티스 관절염</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="5" t="n">
         <v>42979</v>
       </c>
     </row>
@@ -2640,7 +2896,7 @@
           <t>동맥경화·혈전</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="5" t="n">
         <v>42986</v>
       </c>
     </row>
@@ -2665,7 +2921,7 @@
           <t>직장암</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="5" t="n">
         <v>42993</v>
       </c>
     </row>
@@ -2690,7 +2946,7 @@
           <t>갑상선암</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="5" t="n">
         <v>43000</v>
       </c>
     </row>
@@ -2715,7 +2971,7 @@
           <t>경추질환</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="5" t="n">
         <v>43007</v>
       </c>
     </row>
@@ -2740,7 +2996,7 @@
           <t>우울증</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="5" t="n">
         <v>43014</v>
       </c>
     </row>
@@ -2765,7 +3021,7 @@
           <t>통풍</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="5" t="n">
         <v>43021</v>
       </c>
     </row>
@@ -2790,7 +3046,7 @@
           <t>만성통증</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="5" t="n">
         <v>43028</v>
       </c>
     </row>
@@ -2815,7 +3071,7 @@
           <t>간담췌질환·이식</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="5" t="n">
         <v>43035</v>
       </c>
     </row>
@@ -2840,7 +3096,7 @@
           <t>탈모</t>
         </is>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="5" t="n">
         <v>43042</v>
       </c>
     </row>
@@ -2865,7 +3121,7 @@
           <t>어깨 통증</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="5" t="n">
         <v>43049</v>
       </c>
     </row>
@@ -2890,7 +3146,7 @@
           <t>혈관기형</t>
         </is>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="5" t="n">
         <v>43056</v>
       </c>
     </row>
@@ -2915,7 +3171,7 @@
           <t>전립선암·방광암</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="5" t="n">
         <v>43063</v>
       </c>
     </row>
@@ -2940,7 +3196,7 @@
           <t>척추질환</t>
         </is>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="5" t="n">
         <v>43070</v>
       </c>
     </row>
@@ -2965,7 +3221,7 @@
           <t>골다공증</t>
         </is>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="5" t="n">
         <v>43077</v>
       </c>
     </row>
@@ -2990,7 +3246,7 @@
           <t>심혈관질환</t>
         </is>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="5" t="n">
         <v>43084</v>
       </c>
     </row>
@@ -3015,7 +3271,7 @@
           <t>위·식도질환</t>
         </is>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="5" t="n">
         <v>43091</v>
       </c>
     </row>
@@ -3040,7 +3296,7 @@
           <t>미숙아·신생아</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="5" t="n">
         <v>43098</v>
       </c>
     </row>
@@ -3114,7 +3370,7 @@
           <t>비후성 심근증</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>43105</v>
       </c>
     </row>
@@ -3139,7 +3395,7 @@
           <t>뇌출혈·뇌혈관질환</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>43112</v>
       </c>
     </row>
@@ -3164,7 +3420,7 @@
           <t>폐질환·폐암</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>43119</v>
       </c>
     </row>
@@ -3189,7 +3445,7 @@
           <t>간질환</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>43126</v>
       </c>
     </row>
@@ -3214,7 +3470,7 @@
           <t>장질환</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>43133</v>
       </c>
     </row>
@@ -3239,7 +3495,7 @@
           <t>여성암·갱년기</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>43140</v>
       </c>
     </row>
@@ -3264,7 +3520,7 @@
           <t>눈 질환</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>43147</v>
       </c>
     </row>
@@ -3289,7 +3545,7 @@
           <t>치매</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>43154</v>
       </c>
     </row>
@@ -3314,7 +3570,7 @@
           <t>침샘종양·침샘암</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="5" t="n">
         <v>43161</v>
       </c>
     </row>
@@ -3339,7 +3595,7 @@
           <t>담석·결석</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="5" t="n">
         <v>43168</v>
       </c>
     </row>
@@ -3364,7 +3620,7 @@
           <t>코 질환·호흡기</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="5" t="n">
         <v>43175</v>
       </c>
     </row>
@@ -3389,7 +3645,7 @@
           <t>식도암</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="5" t="n">
         <v>43182</v>
       </c>
     </row>
@@ -3414,7 +3670,7 @@
           <t>고관절</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="5" t="n">
         <v>43189</v>
       </c>
     </row>
@@ -3439,7 +3695,7 @@
           <t>담낭암·담도암</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="5" t="n">
         <v>43196</v>
       </c>
     </row>
@@ -3464,7 +3720,7 @@
           <t>다리 혈관질환</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="5" t="n">
         <v>43203</v>
       </c>
     </row>
@@ -3489,7 +3745,7 @@
           <t>수면장애</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="5" t="n">
         <v>43210</v>
       </c>
     </row>
@@ -3514,7 +3770,7 @@
           <t>무릎 골관절염</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="5" t="n">
         <v>43217</v>
       </c>
     </row>
@@ -3539,7 +3795,7 @@
           <t>소아정형 질환</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="5" t="n">
         <v>43224</v>
       </c>
     </row>
@@ -3564,7 +3820,7 @@
           <t>소아암</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="5" t="n">
         <v>43231</v>
       </c>
     </row>
@@ -3589,7 +3845,7 @@
           <t>소아 뇌전증</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="5" t="n">
         <v>43238</v>
       </c>
     </row>
@@ -3614,7 +3870,7 @@
           <t>소아심장질환</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="5" t="n">
         <v>43245</v>
       </c>
     </row>
@@ -3639,7 +3895,7 @@
           <t>전당뇨</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="5" t="n">
         <v>43252</v>
       </c>
     </row>
@@ -3664,7 +3920,7 @@
           <t>췌장 질환</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="5" t="n">
         <v>43259</v>
       </c>
     </row>
@@ -3689,7 +3945,7 @@
           <t>표적항암치료</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="5" t="n">
         <v>43266</v>
       </c>
     </row>
@@ -3714,7 +3970,7 @@
           <t>치주질환·임플란트</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="5" t="n">
         <v>43273</v>
       </c>
     </row>
@@ -3739,7 +3995,7 @@
           <t>유방암 재발</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="5" t="n">
         <v>43287</v>
       </c>
     </row>
@@ -3764,7 +4020,7 @@
           <t>갑상선 질환</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="5" t="n">
         <v>43294</v>
       </c>
     </row>
@@ -3789,7 +4045,7 @@
           <t>이상운동질환</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="5" t="n">
         <v>43301</v>
       </c>
     </row>
@@ -3814,7 +4070,7 @@
           <t>신장·췌장이식</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="5" t="n">
         <v>43308</v>
       </c>
     </row>
@@ -3839,7 +4095,7 @@
           <t>운동 손상·무릎</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="5" t="n">
         <v>43315</v>
       </c>
     </row>
@@ -3864,7 +4120,7 @@
           <t>대동맥류</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="5" t="n">
         <v>43322</v>
       </c>
     </row>
@@ -3889,7 +4145,7 @@
           <t>턱 교정</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="5" t="n">
         <v>43329</v>
       </c>
     </row>
@@ -3914,7 +4170,7 @@
           <t>손목터널증후군</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="5" t="n">
         <v>43343</v>
       </c>
     </row>
@@ -3939,7 +4195,7 @@
           <t>족부 질환</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="5" t="n">
         <v>43350</v>
       </c>
     </row>
@@ -3964,7 +4220,7 @@
           <t>통풍</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="5" t="n">
         <v>43357</v>
       </c>
     </row>
@@ -3989,7 +4245,7 @@
           <t>배뇨장애</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="5" t="n">
         <v>43364</v>
       </c>
     </row>
@@ -4014,7 +4270,7 @@
           <t>자궁내막암</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="5" t="n">
         <v>43371</v>
       </c>
     </row>
@@ -4039,7 +4295,7 @@
           <t>흑색종</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="5" t="n">
         <v>43378</v>
       </c>
     </row>
@@ -4064,7 +4320,7 @@
           <t>대상포진</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="5" t="n">
         <v>43385</v>
       </c>
     </row>
@@ -4089,7 +4345,7 @@
           <t>만성 신장염</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="5" t="n">
         <v>43392</v>
       </c>
     </row>
@@ -4114,7 +4370,7 @@
           <t>두경부암</t>
         </is>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="5" t="n">
         <v>43399</v>
       </c>
     </row>
@@ -4139,7 +4395,7 @@
           <t>두통</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="5" t="n">
         <v>43406</v>
       </c>
     </row>
@@ -4164,7 +4420,7 @@
           <t>척추질환</t>
         </is>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="5" t="n">
         <v>43413</v>
       </c>
     </row>
@@ -4189,7 +4445,7 @@
           <t>경추척수증</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="5" t="n">
         <v>43420</v>
       </c>
     </row>
@@ -4214,7 +4470,7 @@
           <t>심근경색·협심증</t>
         </is>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="5" t="n">
         <v>43427</v>
       </c>
     </row>
@@ -4239,7 +4495,7 @@
           <t>신경통</t>
         </is>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="5" t="n">
         <v>43434</v>
       </c>
     </row>
@@ -4264,7 +4520,7 @@
           <t>위염·위암</t>
         </is>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="5" t="n">
         <v>43441</v>
       </c>
     </row>
@@ -4289,7 +4545,7 @@
           <t>뇌혈관질환</t>
         </is>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="5" t="n">
         <v>43448</v>
       </c>
     </row>
@@ -4314,7 +4570,7 @@
           <t>염증성 장질환</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="5" t="n">
         <v>43455</v>
       </c>
     </row>
@@ -4339,7 +4595,7 @@
           <t>파킨슨병</t>
         </is>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="5" t="n">
         <v>43462</v>
       </c>
     </row>
@@ -4413,7 +4669,7 @@
           <t>복부비만</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>43469</v>
       </c>
     </row>
@@ -4438,7 +4694,7 @@
           <t>어지럼증</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>43476</v>
       </c>
     </row>
@@ -4463,7 +4719,7 @@
           <t>선천성 흉벽기형·오목가슴</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>43483</v>
       </c>
     </row>
@@ -4488,7 +4744,7 @@
           <t>만성골반통</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>43490</v>
       </c>
     </row>
@@ -4513,7 +4769,7 @@
           <t>부정맥</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>43497</v>
       </c>
     </row>
@@ -4538,7 +4794,7 @@
           <t>떨림·뇌수술</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>43504</v>
       </c>
     </row>
@@ -4563,7 +4819,7 @@
           <t>간이식</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>43511</v>
       </c>
     </row>
@@ -4588,7 +4844,7 @@
           <t>혈액암</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>43518</v>
       </c>
     </row>
@@ -4613,7 +4869,7 @@
           <t>고혈압</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="5" t="n">
         <v>43525</v>
       </c>
     </row>
@@ -4638,7 +4894,7 @@
           <t>고혈당</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="5" t="n">
         <v>43532</v>
       </c>
     </row>
@@ -4663,7 +4919,7 @@
           <t>지방간</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="5" t="n">
         <v>43539</v>
       </c>
     </row>
@@ -4688,7 +4944,7 @@
           <t>고지혈증</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="5" t="n">
         <v>43546</v>
       </c>
     </row>
@@ -4713,7 +4969,7 @@
           <t>췌장 질환</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="5" t="n">
         <v>43553</v>
       </c>
     </row>
@@ -4738,7 +4994,7 @@
           <t>유방 질환</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="5" t="n">
         <v>43560</v>
       </c>
     </row>
@@ -4763,7 +5019,7 @@
           <t>갑상선 질환</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="5" t="n">
         <v>43567</v>
       </c>
     </row>
@@ -4788,7 +5044,7 @@
           <t>자궁 질환</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="5" t="n">
         <v>43574</v>
       </c>
     </row>
@@ -4813,7 +5069,7 @@
           <t>대장 질환</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="5" t="n">
         <v>43581</v>
       </c>
     </row>
@@ -4838,7 +5094,7 @@
           <t>퇴행성 무릎 관절염</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="5" t="n">
         <v>43588</v>
       </c>
     </row>
@@ -4863,7 +5119,7 @@
           <t>건선</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="5" t="n">
         <v>43595</v>
       </c>
     </row>
@@ -4888,7 +5144,7 @@
           <t>만성피로증후군</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="5" t="n">
         <v>43602</v>
       </c>
     </row>
@@ -4913,7 +5169,7 @@
           <t>어깨 통증</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="5" t="n">
         <v>43609</v>
       </c>
     </row>
@@ -4938,7 +5194,7 @@
           <t>임플란트</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="5" t="n">
         <v>43616</v>
       </c>
     </row>
@@ -4963,7 +5219,7 @@
           <t>다리 혈관질환</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="5" t="n">
         <v>43623</v>
       </c>
     </row>
@@ -4988,7 +5244,7 @@
           <t>담석·간질환</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="5" t="n">
         <v>43630</v>
       </c>
     </row>
@@ -5013,7 +5269,7 @@
           <t>간염</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="5" t="n">
         <v>43637</v>
       </c>
     </row>
@@ -5038,7 +5294,7 @@
           <t>골감소증</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="5" t="n">
         <v>43644</v>
       </c>
     </row>
@@ -5063,7 +5319,7 @@
           <t>허리 통증</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="5" t="n">
         <v>43651</v>
       </c>
     </row>
@@ -5088,7 +5344,7 @@
           <t>뇌종양</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="5" t="n">
         <v>43658</v>
       </c>
     </row>
@@ -5113,7 +5369,7 @@
           <t>고관절 질환</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="5" t="n">
         <v>43665</v>
       </c>
     </row>
@@ -5138,7 +5394,7 @@
           <t>수면장애</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="5" t="n">
         <v>43672</v>
       </c>
     </row>
@@ -5163,7 +5419,7 @@
           <t>안면신경 질환</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="5" t="n">
         <v>43679</v>
       </c>
     </row>
@@ -5188,7 +5444,7 @@
           <t>경추질환</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="5" t="n">
         <v>43686</v>
       </c>
     </row>
@@ -5213,7 +5469,7 @@
           <t>신장이식</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="5" t="n">
         <v>43693</v>
       </c>
     </row>
@@ -5238,7 +5494,7 @@
           <t>경도인지장애</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="5" t="n">
         <v>43707</v>
       </c>
     </row>
@@ -5263,7 +5519,7 @@
           <t>발 질환</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="5" t="n">
         <v>43714</v>
       </c>
     </row>
@@ -5288,7 +5544,7 @@
           <t>호흡기 질환</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="5" t="n">
         <v>43721</v>
       </c>
     </row>
@@ -5313,7 +5569,7 @@
           <t>아토피</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="5" t="n">
         <v>43728</v>
       </c>
     </row>
@@ -5338,7 +5594,7 @@
           <t>피부 노화</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="5" t="n">
         <v>43735</v>
       </c>
     </row>
@@ -5363,7 +5619,7 @@
           <t>대장암</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="5" t="n">
         <v>43742</v>
       </c>
     </row>
@@ -5388,7 +5644,7 @@
           <t>위염·위암</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="5" t="n">
         <v>43749</v>
       </c>
     </row>
@@ -5413,7 +5669,7 @@
           <t>심장판막증</t>
         </is>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="5" t="n">
         <v>43756</v>
       </c>
     </row>
@@ -5438,7 +5694,7 @@
           <t>피부암</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="5" t="n">
         <v>43763</v>
       </c>
     </row>
@@ -5463,7 +5719,7 @@
           <t>고지혈증</t>
         </is>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="5" t="n">
         <v>43770</v>
       </c>
     </row>
@@ -5488,7 +5744,7 @@
           <t>알코올성 간질환</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="5" t="n">
         <v>43777</v>
       </c>
     </row>
@@ -5513,7 +5769,7 @@
           <t>대상포진</t>
         </is>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="5" t="n">
         <v>43784</v>
       </c>
     </row>
@@ -5538,7 +5794,7 @@
           <t>고혈압·당뇨</t>
         </is>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="5" t="n">
         <v>43791</v>
       </c>
     </row>
@@ -5563,7 +5819,7 @@
           <t>췌장암</t>
         </is>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="5" t="n">
         <v>43798</v>
       </c>
     </row>
@@ -5588,7 +5844,7 @@
           <t>뇌동맥류</t>
         </is>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="5" t="n">
         <v>43805</v>
       </c>
     </row>
@@ -5613,7 +5869,7 @@
           <t>심부전</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="5" t="n">
         <v>43812</v>
       </c>
     </row>
@@ -5638,7 +5894,7 @@
           <t>갱년기</t>
         </is>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="5" t="n">
         <v>43819</v>
       </c>
     </row>
@@ -5663,7 +5919,7 @@
           <t>노안·백내장</t>
         </is>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="5" t="n">
         <v>43826</v>
       </c>
     </row>
@@ -5737,7 +5993,7 @@
           <t>난임</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>43833</v>
       </c>
     </row>
@@ -5762,7 +6018,7 @@
           <t>퇴행성 무릎 관절염</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>43840</v>
       </c>
     </row>
@@ -5787,7 +6043,7 @@
           <t>비만·중성지방</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>43847</v>
       </c>
     </row>
@@ -5812,7 +6068,7 @@
           <t>도서지역 의료</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>43854</v>
       </c>
     </row>
@@ -5837,7 +6093,7 @@
           <t>낙상·골절</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>43861</v>
       </c>
     </row>
@@ -5862,7 +6118,7 @@
           <t>폐렴·독감</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>43868</v>
       </c>
     </row>
@@ -5887,7 +6143,7 @@
           <t>심혈관질환</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>43875</v>
       </c>
     </row>
@@ -5912,7 +6168,7 @@
           <t>비흡연 폐암</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>43882</v>
       </c>
     </row>
@@ -5937,7 +6193,7 @@
           <t>대상포진·흑색종·통풍</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="5" t="n">
         <v>43889</v>
       </c>
     </row>
@@ -5962,7 +6218,7 @@
           <t>고혈압·고지혈증·당뇨</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="5" t="n">
         <v>43896</v>
       </c>
     </row>
@@ -5987,7 +6243,7 @@
           <t>만성 콩팥병</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="5" t="n">
         <v>43903</v>
       </c>
     </row>
@@ -6012,7 +6268,7 @@
           <t>간질환</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="5" t="n">
         <v>43910</v>
       </c>
     </row>
@@ -6037,7 +6293,7 @@
           <t>치매·파킨슨병</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="5" t="n">
         <v>43917</v>
       </c>
     </row>
@@ -6062,7 +6318,7 @@
           <t>뇌졸중</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="5" t="n">
         <v>43924</v>
       </c>
     </row>
@@ -6087,7 +6343,7 @@
           <t>무릎·척추 통증</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="5" t="n">
         <v>43931</v>
       </c>
     </row>
@@ -6112,7 +6368,7 @@
           <t>뇌혈관·심혈관 질환</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="5" t="n">
         <v>43938</v>
       </c>
     </row>
@@ -6137,7 +6393,7 @@
           <t>골감소증·낙상</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="5" t="n">
         <v>43945</v>
       </c>
     </row>
@@ -6162,7 +6418,7 @@
           <t>무릎 통증</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="5" t="n">
         <v>43952</v>
       </c>
     </row>
@@ -6187,7 +6443,7 @@
           <t>뇌종양</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="5" t="n">
         <v>43959</v>
       </c>
     </row>
@@ -6212,7 +6468,7 @@
           <t>부정맥·심장판막</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="5" t="n">
         <v>43966</v>
       </c>
     </row>
@@ -6237,7 +6493,7 @@
           <t>뇌수술</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="5" t="n">
         <v>43973</v>
       </c>
     </row>
@@ -6262,7 +6518,7 @@
           <t>복부비만</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="5" t="n">
         <v>43980</v>
       </c>
     </row>
@@ -6287,7 +6543,7 @@
           <t>어지럼증·만성피로</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="5" t="n">
         <v>43987</v>
       </c>
     </row>
@@ -6312,7 +6568,7 @@
           <t>통풍</t>
         </is>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="5" t="n">
         <v>43994</v>
       </c>
     </row>
@@ -6337,7 +6593,7 @@
           <t>고혈압·당뇨</t>
         </is>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="5" t="n">
         <v>44001</v>
       </c>
     </row>
@@ -6362,7 +6618,7 @@
           <t>고관절 질환</t>
         </is>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="E27" s="5" t="n">
         <v>44008</v>
       </c>
     </row>
@@ -6387,7 +6643,7 @@
           <t>췌장암·담도암·담낭암</t>
         </is>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="5" t="n">
         <v>44015</v>
       </c>
     </row>
@@ -6412,7 +6668,7 @@
           <t>간이식·간경화</t>
         </is>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="5" t="n">
         <v>44022</v>
       </c>
     </row>
@@ -6437,7 +6693,7 @@
           <t>두통</t>
         </is>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="5" t="n">
         <v>44029</v>
       </c>
     </row>
@@ -6462,7 +6718,7 @@
           <t>위염·조기위암</t>
         </is>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="5" t="n">
         <v>44036</v>
       </c>
     </row>
@@ -6487,7 +6743,7 @@
           <t>변비·설사·장질환</t>
         </is>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="5" t="n">
         <v>44043</v>
       </c>
     </row>
@@ -6512,7 +6768,7 @@
           <t>지방간</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="5" t="n">
         <v>44050</v>
       </c>
     </row>
@@ -6537,7 +6793,7 @@
           <t>흑색종</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="5" t="n">
         <v>44057</v>
       </c>
     </row>
@@ -6562,7 +6818,7 @@
           <t>탈모</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="5" t="n">
         <v>44071</v>
       </c>
     </row>
@@ -6587,7 +6843,7 @@
           <t>어깨질환</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="5" t="n">
         <v>44078</v>
       </c>
     </row>
@@ -6612,7 +6868,7 @@
           <t>간염·간암</t>
         </is>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="5" t="n">
         <v>44085</v>
       </c>
     </row>
@@ -6637,7 +6893,7 @@
           <t>안면신경질환</t>
         </is>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="5" t="n">
         <v>44092</v>
       </c>
     </row>
@@ -6662,7 +6918,7 @@
           <t>호르몬 불균형</t>
         </is>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="5" t="n">
         <v>44099</v>
       </c>
     </row>
@@ -6687,7 +6943,7 @@
           <t>심장질환·심장마비</t>
         </is>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="E40" s="5" t="n">
         <v>44106</v>
       </c>
     </row>
@@ -6712,7 +6968,7 @@
           <t>피부 노화</t>
         </is>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="5" t="n">
         <v>44113</v>
       </c>
     </row>
@@ -6737,7 +6993,7 @@
           <t>고지혈증·동맥경화</t>
         </is>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="5" t="n">
         <v>44120</v>
       </c>
     </row>
@@ -6762,7 +7018,7 @@
           <t>대장암</t>
         </is>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="5" t="n">
         <v>44127</v>
       </c>
     </row>
@@ -6787,7 +7043,7 @@
           <t>다리 혈관질환</t>
         </is>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="5" t="n">
         <v>44134</v>
       </c>
     </row>
@@ -6812,7 +7068,7 @@
           <t>무릎 골관절염</t>
         </is>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="5" t="n">
         <v>44141</v>
       </c>
     </row>
@@ -6837,7 +7093,7 @@
           <t>갑상선암</t>
         </is>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="5" t="n">
         <v>44148</v>
       </c>
     </row>
@@ -6862,7 +7118,7 @@
           <t>폐암</t>
         </is>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="E47" s="5" t="n">
         <v>44155</v>
       </c>
     </row>
@@ -6887,7 +7143,7 @@
           <t>위암</t>
         </is>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="E48" s="5" t="n">
         <v>44162</v>
       </c>
     </row>
@@ -6912,7 +7168,7 @@
           <t>경추 척수증</t>
         </is>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="E49" s="5" t="n">
         <v>44169</v>
       </c>
     </row>
@@ -6937,7 +7193,7 @@
           <t>만성 콩팥병</t>
         </is>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="E50" s="5" t="n">
         <v>44176</v>
       </c>
     </row>
@@ -6962,7 +7218,7 @@
           <t>통풍</t>
         </is>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="E51" s="5" t="n">
         <v>44183</v>
       </c>
     </row>
@@ -6987,7 +7243,7 @@
           <t>뇌종양</t>
         </is>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="E52" s="5" t="n">
         <v>44190</v>
       </c>
     </row>
